--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1372,981 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128918202</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97503</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>486754</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7006298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128918564</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>486599</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7006173</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128918415</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>486640</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7006215</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128918663</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>486577</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7006161</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128918585</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>486598</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7006169</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128918341</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92201</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>486673</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7006224</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128918694</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>486533</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7006118</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128918473</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>486633</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7006201</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128918200</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>486701</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7006242</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515052</v>
       </c>
       <c r="B2" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128514987</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91511</v>
+        <v>91516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91511</v>
+        <v>91516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91511</v>
+        <v>91516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128546288</v>
       </c>
       <c r="B4" t="n">
-        <v>91516</v>
+        <v>91522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128546287</v>
       </c>
       <c r="B5" t="n">
-        <v>92218</v>
+        <v>92226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128546295</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128546294</v>
       </c>
       <c r="B7" t="n">
-        <v>91516</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128546293</v>
       </c>
       <c r="B8" t="n">
-        <v>91516</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>128918202</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128918564</v>
       </c>
       <c r="B10" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128918415</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128918663</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128918585</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>128918341</v>
       </c>
       <c r="B14" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128918694</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128918473</v>
       </c>
       <c r="B16" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128918200</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -2349,7 +2349,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133823472</v>
+        <v>133823469</v>
       </c>
       <c r="B18" t="n">
         <v>91956</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486629</v>
+        <v>486534</v>
       </c>
       <c r="R18" t="n">
-        <v>7006201</v>
+        <v>7006114</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2456,7 +2456,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133823469</v>
+        <v>133823472</v>
       </c>
       <c r="B19" t="n">
         <v>91956</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486534</v>
+        <v>486629</v>
       </c>
       <c r="R19" t="n">
-        <v>7006114</v>
+        <v>7006201</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -2352,7 +2352,7 @@
         <v>133823469</v>
       </c>
       <c r="B18" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>133823472</v>
       </c>
       <c r="B19" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128515052</v>
+        <v>128546288</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nilsvallen, Jmt</t>
+          <t>Spikbodarna önö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486537</v>
+        <v>486531</v>
       </c>
       <c r="R2" t="n">
-        <v>7006130</v>
+        <v>7006117</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128514987</v>
+        <v>128546293</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Spikbodarna önö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486599</v>
+        <v>486706</v>
       </c>
       <c r="R3" t="n">
-        <v>7006160</v>
+        <v>7006248</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +840,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128546288</v>
+        <v>128546294</v>
       </c>
       <c r="B4" t="n">
-        <v>91522</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486531</v>
+        <v>486634</v>
       </c>
       <c r="R4" t="n">
-        <v>7006117</v>
+        <v>7006206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128546287</v>
+        <v>128918200</v>
       </c>
       <c r="B5" t="n">
-        <v>92226</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spikbodarna önö, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486669</v>
+        <v>486701</v>
       </c>
       <c r="R5" t="n">
-        <v>7006226</v>
+        <v>7006242</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128546295</v>
+        <v>128918415</v>
       </c>
       <c r="B6" t="n">
-        <v>91544</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spikbodarna önö, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486515</v>
+        <v>486640</v>
       </c>
       <c r="R6" t="n">
-        <v>7006115</v>
+        <v>7006215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128546294</v>
+        <v>128918473</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spikbodarna önö, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486634</v>
+        <v>486633</v>
       </c>
       <c r="R7" t="n">
-        <v>7006206</v>
+        <v>7006201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128546293</v>
+        <v>128918585</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,14 +1318,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spikbodarna önö, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486706</v>
+        <v>486598</v>
       </c>
       <c r="R8" t="n">
-        <v>7006248</v>
+        <v>7006169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,12 +1352,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,61 +1382,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128918202</v>
+        <v>128918587</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nilsvallen, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486754</v>
+        <v>486589</v>
       </c>
       <c r="R9" t="n">
-        <v>7006298</v>
+        <v>7006177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1458,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,44 +1489,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128918564</v>
+        <v>128918663</v>
       </c>
       <c r="B10" t="n">
-        <v>92267</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486599</v>
+        <v>486577</v>
       </c>
       <c r="R10" t="n">
-        <v>7006173</v>
+        <v>7006161</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1555,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1565,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918415</v>
+        <v>128918694</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,20 +1636,24 @@
           <t>(Fr.) Krieglst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486640</v>
+        <v>486533</v>
       </c>
       <c r="R11" t="n">
-        <v>7006215</v>
+        <v>7006118</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1662,7 +1682,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1672,7 +1692,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1687,22 +1707,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128918663</v>
+        <v>131685191</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,17 +1750,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486577</v>
+        <v>486715</v>
       </c>
       <c r="R12" t="n">
-        <v>7006161</v>
+        <v>7006283</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,22 +1784,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128918585</v>
+        <v>131685292</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>91970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,14 +1857,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486598</v>
+        <v>486707</v>
       </c>
       <c r="R13" t="n">
-        <v>7006169</v>
+        <v>7006274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,22 +1891,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,64 +1921,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128918341</v>
+        <v>133823469</v>
       </c>
       <c r="B14" t="n">
-        <v>92267</v>
+        <v>91970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486673</v>
+        <v>486534</v>
       </c>
       <c r="R14" t="n">
-        <v>7006224</v>
+        <v>7006114</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,22 +1998,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918694</v>
+        <v>133823470</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2068,17 @@
           <t>(Fr.) Krieglst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nilsvallen, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486533</v>
+        <v>486514</v>
       </c>
       <c r="R15" t="n">
-        <v>7006118</v>
+        <v>7006160</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2093,22 +2105,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,22 +2135,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918473</v>
+        <v>133823472</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>91970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,17 +2178,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486633</v>
+        <v>486629</v>
       </c>
       <c r="R16" t="n">
         <v>7006201</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,22 +2212,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,22 +2242,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128918200</v>
+        <v>133823473</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2273,17 +2285,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nilsvallen, Nilsvallen, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486701</v>
+        <v>486704</v>
       </c>
       <c r="R17" t="n">
-        <v>7006242</v>
+        <v>7006239</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,22 +2319,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,60 +2349,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133823469</v>
+        <v>128546287</v>
       </c>
       <c r="B18" t="n">
-        <v>91963</v>
+        <v>92632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spikbodarna, Jmt</t>
+          <t>Spikbodarna önö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486534</v>
+        <v>486669</v>
       </c>
       <c r="R18" t="n">
-        <v>7006114</v>
+        <v>7006226</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,22 +2426,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,60 +2446,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133823472</v>
+        <v>128918341</v>
       </c>
       <c r="B19" t="n">
-        <v>91963</v>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spikbodarna, Jmt</t>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486629</v>
+        <v>486673</v>
       </c>
       <c r="R19" t="n">
-        <v>7006201</v>
+        <v>7006224</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2521,22 +2527,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2560,6 +2566,772 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128918564</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>486599</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7006173</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131814642</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>486501</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7006121</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131818000</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>486715</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7006283</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128514960</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>486609</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7006164</v>
+      </c>
+      <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128514987</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>486599</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7006160</v>
+      </c>
+      <c r="S24" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128515052</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>486537</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7006130</v>
+      </c>
+      <c r="S25" t="n">
+        <v>30</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128918112</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nilsvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>486754</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7006298</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41493-2025 artfynd.xlsx
+++ b/artfynd/A 41493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546288</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546294</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918473</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918585</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918663</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918694</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131685191</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131685292</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823469</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823470</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823472</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823473</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918341</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2673,6 +2768,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918564</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131814642</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131818000</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3007,6 +3117,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514960</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3114,6 +3229,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514987</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3221,6 +3341,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128515052</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3332,8 +3457,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>